--- a/exports/NAUKRI_full_report.xlsx
+++ b/exports/NAUKRI_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q79"/>
+  <dimension ref="A1:U79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>4.14</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44579.55208333334</v>
+        <v>44580.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>1074</v>
+        <v>1026.5</v>
       </c>
       <c r="I2" t="n">
         <v>1073.735504942613</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.55</v>
+        <v>-7.81</v>
       </c>
       <c r="L2" t="n">
-        <v>5.34</v>
+        <v>8.4</v>
       </c>
       <c r="M2" t="n">
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>4.79</v>
+        <v>6.33</v>
       </c>
       <c r="O2" t="n">
         <v>-0.98</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>10.26</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44589.55208333334</v>
+        <v>44592.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>879</v>
+        <v>977.5</v>
       </c>
       <c r="I3" t="n">
         <v>976.2558204884983</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K3" t="n">
-        <v>14.37</v>
+        <v>4.77</v>
       </c>
       <c r="L3" t="n">
         <v>4.72</v>
       </c>
       <c r="M3" t="n">
-        <v>0.91</v>
+        <v>4.44</v>
       </c>
       <c r="N3" t="n">
-        <v>1.28</v>
+        <v>11.72</v>
       </c>
       <c r="O3" t="n">
         <v>-6.33</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>15.79</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44603.38541666666</v>
+        <v>44603.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>922.5</v>
+        <v>917</v>
       </c>
       <c r="I4" t="n">
         <v>920.2840906705553</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K4" t="n">
-        <v>-5.63</v>
+        <v>-6.19</v>
       </c>
       <c r="L4" t="n">
         <v>6.65</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>9.49</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44622.55208333334</v>
+        <v>44623.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>914</v>
+        <v>925.5</v>
       </c>
       <c r="I5" t="n">
         <v>924.8241000262913</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>0.33</v>
+        <v>-0.93</v>
       </c>
       <c r="L5" t="n">
         <v>3.16</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>7.47</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44648.38541666666</v>
+        <v>44648.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>886.5</v>
+        <v>880</v>
       </c>
       <c r="I6" t="n">
         <v>882.1385347544101</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>25</v>
+        <v>25.16666666666667</v>
       </c>
       <c r="K6" t="n">
-        <v>-4.21</v>
+        <v>-4.92</v>
       </c>
       <c r="L6" t="n">
         <v>9.02</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,25 +902,25 @@
         <v>7.31</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44655.55208333334</v>
+        <v>44656.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>935.5</v>
+        <v>957.5</v>
       </c>
       <c r="I7" t="n">
         <v>944.350750280781</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.31</v>
+        <v>-8.81</v>
       </c>
       <c r="L7" t="n">
-        <v>6.88</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>0.61</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N7" t="n">
         <v>2.67</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>7.09</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44664.55208333334</v>
+        <v>44669.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>953.5</v>
+        <v>923</v>
       </c>
       <c r="I8" t="n">
         <v>926.5932044054396</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>13</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.42</v>
+        <v>-3.6</v>
       </c>
       <c r="L8" t="n">
-        <v>2.61</v>
+        <v>3.81</v>
       </c>
       <c r="M8" t="n">
-        <v>-0</v>
+        <v>0.89</v>
       </c>
       <c r="N8" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="O8" t="n">
         <v>0.91</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>7</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44708.55208333334</v>
+        <v>44711.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>737</v>
+        <v>761.5</v>
       </c>
       <c r="I9" t="n">
         <v>739.3386562045375</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K9" t="n">
-        <v>20.15</v>
+        <v>17.5</v>
       </c>
       <c r="L9" t="n">
         <v>5.42</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>9.49</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44715.55208333334</v>
+        <v>44718.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>769.5</v>
+        <v>742</v>
       </c>
       <c r="I10" t="n">
         <v>753.9461413863852</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K10" t="n">
-        <v>1.05</v>
+        <v>-2.56</v>
       </c>
       <c r="L10" t="n">
-        <v>2.23</v>
+        <v>3.61</v>
       </c>
       <c r="M10" t="n">
         <v>0.61</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>11.23</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44735.55208333334</v>
+        <v>44736.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>750</v>
+        <v>783.5</v>
       </c>
       <c r="I11" t="n">
         <v>769.10473246749</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.08</v>
+        <v>-5.59</v>
       </c>
       <c r="L11" t="n">
-        <v>3.23</v>
+        <v>6.74</v>
       </c>
       <c r="M11" t="n">
         <v>1.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.77</v>
+        <v>4.07</v>
       </c>
       <c r="O11" t="n">
         <v>-3.51</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>8.710000000000001</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44767.55208333334</v>
+        <v>44768.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>802.5</v>
+        <v>785</v>
       </c>
       <c r="I12" t="n">
         <v>785.9128189294623</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K12" t="n">
-        <v>2.43</v>
+        <v>0.19</v>
       </c>
       <c r="L12" t="n">
         <v>7.91</v>
@@ -1125,7 +1268,7 @@
         <v>1.13</v>
       </c>
       <c r="N12" t="n">
-        <v>2.83</v>
+        <v>3.99</v>
       </c>
       <c r="O12" t="n">
         <v>4.07</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>8</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44770.55208333334</v>
+        <v>44771.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>819</v>
+        <v>845</v>
       </c>
       <c r="I13" t="n">
         <v>825.3445710816563</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.33</v>
+        <v>-7.64</v>
       </c>
       <c r="L13" t="n">
-        <v>4.46</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="M13" t="n">
         <v>1.25</v>
       </c>
       <c r="N13" t="n">
-        <v>4.46</v>
+        <v>5.8</v>
       </c>
       <c r="O13" t="n">
         <v>-3.99</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>7.92</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44799.55208333334</v>
+        <v>44802.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>888</v>
+        <v>831.5</v>
       </c>
       <c r="I14" t="n">
         <v>844.959292731941</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K14" t="n">
-        <v>5.09</v>
+        <v>-1.6</v>
       </c>
       <c r="L14" t="n">
         <v>3.31</v>
       </c>
       <c r="M14" t="n">
-        <v>1.83</v>
+        <v>5.35</v>
       </c>
       <c r="N14" t="n">
-        <v>5.31</v>
+        <v>6.53</v>
       </c>
       <c r="O14" t="n">
         <v>5.8</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>11.1</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44875.55208333334</v>
+        <v>44876.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>765</v>
+        <v>806</v>
       </c>
       <c r="I15" t="n">
         <v>799.5360659450648</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>73.16666666666667</v>
+        <v>74</v>
       </c>
       <c r="K15" t="n">
-        <v>8</v>
+        <v>3.07</v>
       </c>
       <c r="L15" t="n">
         <v>5.65</v>
       </c>
       <c r="M15" t="n">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="N15" t="n">
-        <v>5.26</v>
+        <v>7.19</v>
       </c>
       <c r="O15" t="n">
         <v>-6.53</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>6.93</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44881.55208333334</v>
+        <v>44882.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>829</v>
+        <v>791</v>
       </c>
       <c r="I16" t="n">
         <v>809.0367185389666</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K16" t="n">
-        <v>2.85</v>
+        <v>-1.86</v>
       </c>
       <c r="L16" t="n">
         <v>2.98</v>
       </c>
       <c r="M16" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="N16" t="n">
-        <v>4.21</v>
+        <v>5.73</v>
       </c>
       <c r="O16" t="n">
         <v>7.19</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>10.51</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44907.55208333334</v>
+        <v>44908.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>810</v>
+        <v>829</v>
       </c>
       <c r="I17" t="n">
         <v>816.5573943503091</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.4</v>
+        <v>-4.8</v>
       </c>
       <c r="L17" t="n">
-        <v>4.68</v>
+        <v>6.45</v>
       </c>
       <c r="M17" t="n">
         <v>1.38</v>
       </c>
       <c r="N17" t="n">
-        <v>2.13</v>
+        <v>2.72</v>
       </c>
       <c r="O17" t="n">
         <v>-5.73</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>5.45</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44917.55208333334</v>
+        <v>44918.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>812.5</v>
+        <v>781.5</v>
       </c>
       <c r="I18" t="n">
         <v>800.2754842107007</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.99</v>
+        <v>-5.73</v>
       </c>
       <c r="L18" t="n">
-        <v>2.9</v>
+        <v>6.03</v>
       </c>
       <c r="M18" t="n">
         <v>0.85</v>
       </c>
       <c r="N18" t="n">
-        <v>2.17</v>
+        <v>5.35</v>
       </c>
       <c r="O18" t="n">
         <v>2.72</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>9.960000000000001</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44966.38541666666</v>
+        <v>44966.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>758</v>
+        <v>766</v>
       </c>
       <c r="I19" t="n">
         <v>765.5318204355491</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>48</v>
+        <v>48.16666666666666</v>
       </c>
       <c r="K19" t="n">
-        <v>3.01</v>
+        <v>1.98</v>
       </c>
       <c r="L19" t="n">
         <v>3.84</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>6.18</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44967.55208333334</v>
+        <v>44970.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>765</v>
+        <v>681</v>
       </c>
       <c r="I20" t="n">
         <v>721.1633817306049</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.13</v>
+        <v>-11.1</v>
       </c>
       <c r="L20" t="n">
-        <v>2.02</v>
+        <v>12.53</v>
       </c>
       <c r="M20" t="n">
-        <v>0.13</v>
+        <v>1.96</v>
       </c>
       <c r="N20" t="n">
-        <v>0.13</v>
+        <v>9.74</v>
       </c>
       <c r="O20" t="n">
         <v>1.06</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>14.24</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45009.55208333334</v>
+        <v>45012.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>693</v>
+        <v>710</v>
       </c>
       <c r="I21" t="n">
         <v>709.3551406479064</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.76</v>
+        <v>-4.26</v>
       </c>
       <c r="L21" t="n">
         <v>10.13</v>
@@ -1638,7 +1889,7 @@
         <v>1.22</v>
       </c>
       <c r="N21" t="n">
-        <v>1.82</v>
+        <v>2.81</v>
       </c>
       <c r="O21" t="n">
         <v>-9.74</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>6.32</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45029.55208333334</v>
+        <v>45033.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>762</v>
+        <v>730.5</v>
       </c>
       <c r="I22" t="n">
         <v>738.9445672480289</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K22" t="n">
-        <v>7.32</v>
+        <v>2.89</v>
       </c>
       <c r="L22" t="n">
         <v>2.25</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="N22" t="n">
-        <v>1.99</v>
+        <v>3.54</v>
       </c>
       <c r="O22" t="n">
         <v>2.81</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>6.37</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45044.55208333334</v>
+        <v>45048.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>753.5</v>
+        <v>756.5</v>
       </c>
       <c r="I23" t="n">
         <v>754.7488488521866</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.15</v>
+        <v>-3.56</v>
       </c>
       <c r="L23" t="n">
         <v>3.83</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>4.08</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45063.55208333334</v>
+        <v>45064.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>767</v>
+        <v>743.5</v>
       </c>
       <c r="I24" t="n">
         <v>760.5595156607463</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K24" t="n">
-        <v>1.39</v>
+        <v>-1.72</v>
       </c>
       <c r="L24" t="n">
-        <v>0.99</v>
+        <v>1.72</v>
       </c>
       <c r="M24" t="n">
         <v>0.39</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>7.91</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45068.55208333334</v>
+        <v>45069.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>778</v>
+        <v>790.5</v>
       </c>
       <c r="I25" t="n">
         <v>788.1079231877374</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.64</v>
+        <v>-6.32</v>
       </c>
       <c r="L25" t="n">
-        <v>4.77</v>
+        <v>7.06</v>
       </c>
       <c r="M25" t="n">
         <v>0.65</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>5.65</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45100.38541666666</v>
+        <v>45100.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>869</v>
+        <v>859</v>
       </c>
       <c r="I26" t="n">
         <v>859.0972928997402</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>31</v>
+        <v>31.16666666666667</v>
       </c>
       <c r="K26" t="n">
-        <v>9.93</v>
+        <v>8.67</v>
       </c>
       <c r="L26" t="n">
         <v>5.5</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>5.54</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45119.55208333334</v>
+        <v>45120.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>892</v>
+        <v>918</v>
       </c>
       <c r="I27" t="n">
         <v>906.5598911284804</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K27" t="n">
-        <v>-3.84</v>
+        <v>-6.87</v>
       </c>
       <c r="L27" t="n">
-        <v>6.29</v>
+        <v>7.1</v>
       </c>
       <c r="M27" t="n">
         <v>0.87</v>
       </c>
       <c r="N27" t="n">
-        <v>2.5</v>
+        <v>3.92</v>
       </c>
       <c r="O27" t="n">
         <v>-2.39</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>6</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45140.55208333334</v>
+        <v>45141.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>915.5</v>
+        <v>898.5</v>
       </c>
       <c r="I28" t="n">
         <v>903.9906264233624</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.27</v>
+        <v>-2.12</v>
       </c>
       <c r="L28" t="n">
         <v>2.72</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>5.16</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45141.55208333334</v>
+        <v>45142.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>905.5</v>
+        <v>958</v>
       </c>
       <c r="I29" t="n">
         <v>944.833296842859</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.78</v>
+        <v>-6.62</v>
       </c>
       <c r="L29" t="n">
-        <v>1.67</v>
+        <v>7.96</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="O29" t="n">
         <v>-1.09</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>7.81</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45149.38541666666</v>
+        <v>45149.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>926.5</v>
+        <v>890.5</v>
       </c>
       <c r="I30" t="n">
         <v>920.5020239414001</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K30" t="n">
-        <v>-3.29</v>
+        <v>-7.05</v>
       </c>
       <c r="L30" t="n">
-        <v>5.22</v>
+        <v>7.78</v>
       </c>
       <c r="M30" t="n">
         <v>0.16</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>8.35</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45167.55208333334</v>
+        <v>45168.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>852</v>
+        <v>879</v>
       </c>
       <c r="I31" t="n">
         <v>866.2160489763065</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>18</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K31" t="n">
-        <v>4.32</v>
+        <v>1.29</v>
       </c>
       <c r="L31" t="n">
         <v>4.04</v>
       </c>
       <c r="M31" t="n">
-        <v>0.66</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N31" t="n">
-        <v>2.35</v>
+        <v>2.52</v>
       </c>
       <c r="O31" t="n">
         <v>-4.25</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>5.57</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45190.55208333334</v>
+        <v>45191.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>886</v>
+        <v>866</v>
       </c>
       <c r="I32" t="n">
         <v>866.0035941789282</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K32" t="n">
-        <v>0.8</v>
+        <v>-1.48</v>
       </c>
       <c r="L32" t="n">
         <v>2.45</v>
@@ -2265,7 +2648,7 @@
         <v>1.28</v>
       </c>
       <c r="N32" t="n">
-        <v>2.06</v>
+        <v>3.27</v>
       </c>
       <c r="O32" t="n">
         <v>2.52</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>6.49</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45209.38541666666</v>
+        <v>45209.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="I33" t="n">
         <v>844.5994577251037</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K33" t="n">
-        <v>2.66</v>
+        <v>2.19</v>
       </c>
       <c r="L33" t="n">
         <v>2.89</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>4.16</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45222.38541666666</v>
+        <v>45222.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>825</v>
+        <v>817.5</v>
       </c>
       <c r="I34" t="n">
         <v>821.4214153414845</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>12.83333333333333</v>
+        <v>13</v>
       </c>
       <c r="K34" t="n">
-        <v>-2.6</v>
+        <v>-3.48</v>
       </c>
       <c r="L34" t="n">
-        <v>3.13</v>
+        <v>4.13</v>
       </c>
       <c r="M34" t="n">
         <v>0.71</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>4.59</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45233.38541666666</v>
+        <v>45233.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>842.5</v>
+        <v>849</v>
       </c>
       <c r="I35" t="n">
         <v>845.2644534772299</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>10.83333333333333</v>
+        <v>11</v>
       </c>
       <c r="K35" t="n">
-        <v>-3.06</v>
+        <v>-3.85</v>
       </c>
       <c r="L35" t="n">
-        <v>3.18</v>
+        <v>4.46</v>
       </c>
       <c r="M35" t="n">
         <v>1.34</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>4.62</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45254.55208333334</v>
+        <v>45258.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>917</v>
+        <v>911.5</v>
       </c>
       <c r="I36" t="n">
         <v>912.2239354069407</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>21</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="K36" t="n">
-        <v>8.01</v>
+        <v>7.36</v>
       </c>
       <c r="L36" t="n">
         <v>0.88</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>4.6</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45265.55208333334</v>
+        <v>45266.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>942</v>
+        <v>950.5</v>
       </c>
       <c r="I37" t="n">
         <v>945.6791075952036</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K37" t="n">
-        <v>-3.35</v>
+        <v>-4.28</v>
       </c>
       <c r="L37" t="n">
-        <v>3.78</v>
+        <v>5.76</v>
       </c>
       <c r="M37" t="n">
         <v>1.03</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>4.31</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45311.55208333334</v>
+        <v>45314.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>1012.5</v>
+        <v>992.5</v>
       </c>
       <c r="I38" t="n">
         <v>1009.161487441962</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>45.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K38" t="n">
-        <v>6.52</v>
+        <v>4.42</v>
       </c>
       <c r="L38" t="n">
         <v>1.74</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>7.38</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45327.55208333334</v>
+        <v>45328.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>1036</v>
+        <v>1061.5</v>
       </c>
       <c r="I39" t="n">
         <v>1042.200618874885</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K39" t="n">
-        <v>-4.38</v>
+        <v>-6.95</v>
       </c>
       <c r="L39" t="n">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="M39" t="n">
         <v>3.23</v>
       </c>
       <c r="N39" t="n">
-        <v>2.81</v>
+        <v>3.33</v>
       </c>
       <c r="O39" t="n">
         <v>-2.57</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>6.69</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45335.55208333334</v>
+        <v>45336.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>1067</v>
+        <v>1011.5</v>
       </c>
       <c r="I40" t="n">
         <v>1046.835709086771</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K40" t="n">
-        <v>0.52</v>
+        <v>-4.71</v>
       </c>
       <c r="L40" t="n">
-        <v>2.45</v>
+        <v>5.18</v>
       </c>
       <c r="M40" t="n">
         <v>0.05</v>
       </c>
       <c r="N40" t="n">
-        <v>1.51</v>
+        <v>4.03</v>
       </c>
       <c r="O40" t="n">
         <v>3.33</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>10.95</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45377.55208333334</v>
+        <v>45378.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>1043.5</v>
+        <v>1092</v>
       </c>
       <c r="I41" t="n">
         <v>1069.117064464377</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K41" t="n">
-        <v>-3.16</v>
+        <v>-7.96</v>
       </c>
       <c r="L41" t="n">
-        <v>7.51</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="M41" t="n">
         <v>1.69</v>
       </c>
       <c r="N41" t="n">
-        <v>4.08</v>
+        <v>4.84</v>
       </c>
       <c r="O41" t="n">
         <v>-4.03</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>8.5</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45397.38541666666</v>
+        <v>45397.55208333334</v>
       </c>
       <c r="H42" t="n">
-        <v>1166.5</v>
+        <v>1166</v>
       </c>
       <c r="I42" t="n">
         <v>1166.065433568261</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K42" t="n">
-        <v>6.82</v>
+        <v>6.78</v>
       </c>
       <c r="L42" t="n">
         <v>4.67</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>6.67</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45408.55208333334</v>
+        <v>45411.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>1180</v>
+        <v>1212.5</v>
       </c>
       <c r="I43" t="n">
         <v>1199.106379965198</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>11</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.2</v>
+        <v>-3.99</v>
       </c>
       <c r="L43" t="n">
-        <v>2.92</v>
+        <v>4.93</v>
       </c>
       <c r="M43" t="n">
         <v>1.32</v>
       </c>
       <c r="N43" t="n">
-        <v>2.15</v>
+        <v>3.22</v>
       </c>
       <c r="O43" t="n">
         <v>-2.51</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>6.19</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45440.55208333334</v>
+        <v>45441.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>1213</v>
+        <v>1194</v>
       </c>
       <c r="I44" t="n">
         <v>1204.102291916691</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K44" t="n">
-        <v>0.04</v>
+        <v>-1.53</v>
       </c>
       <c r="L44" t="n">
         <v>7.46</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>7.77</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45448.55208333334</v>
+        <v>45449.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>1194.5</v>
+        <v>1219</v>
       </c>
       <c r="I45" t="n">
         <v>1210.172993987605</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.04</v>
+        <v>-2.09</v>
       </c>
       <c r="L45" t="n">
-        <v>1.97</v>
+        <v>3.27</v>
       </c>
       <c r="M45" t="n">
         <v>6.38</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>9.710000000000001</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45484.38541666666</v>
+        <v>45484.55208333334</v>
       </c>
       <c r="H46" t="n">
-        <v>1332</v>
+        <v>1320</v>
       </c>
       <c r="I46" t="n">
         <v>1320.385592084733</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K46" t="n">
-        <v>9.27</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="L46" t="n">
         <v>1.56</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>6.23</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45498.38541666666</v>
+        <v>45498.55208333334</v>
       </c>
       <c r="H47" t="n">
-        <v>1376</v>
+        <v>1403</v>
       </c>
       <c r="I47" t="n">
         <v>1402.266439229886</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>13.83333333333333</v>
+        <v>14</v>
       </c>
       <c r="K47" t="n">
-        <v>-4.24</v>
+        <v>-6.29</v>
       </c>
       <c r="L47" t="n">
         <v>7.12</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>6.69</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45538.55208333334</v>
+        <v>45539.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>1492.5</v>
+        <v>1463</v>
       </c>
       <c r="I48" t="n">
         <v>1480.936747789071</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>40</v>
+        <v>40.83333333333334</v>
       </c>
       <c r="K48" t="n">
-        <v>6.38</v>
+        <v>4.28</v>
       </c>
       <c r="L48" t="n">
         <v>3.31</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>4.85</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45545.55208333334</v>
+        <v>45546.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>1495</v>
+        <v>1547</v>
       </c>
       <c r="I49" t="n">
         <v>1534.004764798031</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K49" t="n">
-        <v>-2.19</v>
+        <v>-5.74</v>
       </c>
       <c r="L49" t="n">
-        <v>3.14</v>
+        <v>6.32</v>
       </c>
       <c r="M49" t="n">
         <v>1.18</v>
       </c>
       <c r="N49" t="n">
-        <v>0.71</v>
+        <v>2.24</v>
       </c>
       <c r="O49" t="n">
         <v>-0.8</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>6.26</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45586.38541666666</v>
+        <v>45586.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>1592.5</v>
+        <v>1584</v>
       </c>
       <c r="I50" t="n">
         <v>1587.091313724302</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>40</v>
+        <v>40.16666666666666</v>
       </c>
       <c r="K50" t="n">
-        <v>2.94</v>
+        <v>2.39</v>
       </c>
       <c r="L50" t="n">
         <v>3.33</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>5.32</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45602.38541666666</v>
+        <v>45602.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>1586.5</v>
+        <v>1600</v>
       </c>
       <c r="I51" t="n">
         <v>1589.394066744416</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>15.83333333333333</v>
+        <v>16</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.16</v>
+        <v>-1.01</v>
       </c>
       <c r="L51" t="n">
-        <v>0.73</v>
+        <v>1.17</v>
       </c>
       <c r="M51" t="n">
         <v>0.72</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>6.8</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45646.38541666666</v>
+        <v>45646.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>1717.5</v>
+        <v>1696</v>
       </c>
       <c r="I52" t="n">
         <v>1707.511399797152</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>43.83333333333334</v>
+        <v>44</v>
       </c>
       <c r="K52" t="n">
-        <v>7.34</v>
+        <v>6</v>
       </c>
       <c r="L52" t="n">
         <v>6.38</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>5.72</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45660.38541666666</v>
+        <v>45660.55208333334</v>
       </c>
       <c r="H53" t="n">
-        <v>1781.5</v>
+        <v>1817</v>
       </c>
       <c r="I53" t="n">
         <v>1793.017745593088</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>13.83333333333333</v>
+        <v>14</v>
       </c>
       <c r="K53" t="n">
-        <v>-5.04</v>
+        <v>-7.13</v>
       </c>
       <c r="L53" t="n">
-        <v>6.6</v>
+        <v>7.13</v>
       </c>
       <c r="M53" t="n">
         <v>1.02</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>6.23</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45663.55208333334</v>
+        <v>45664.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>1758</v>
+        <v>1695.5</v>
       </c>
       <c r="I54" t="n">
         <v>1703.746971301891</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>3</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="K54" t="n">
-        <v>-3.25</v>
+        <v>-6.69</v>
       </c>
       <c r="L54" t="n">
-        <v>3.77</v>
+        <v>7.95</v>
       </c>
       <c r="M54" t="n">
-        <v>0.03</v>
+        <v>0.11</v>
       </c>
       <c r="N54" t="n">
-        <v>3.25</v>
+        <v>4.15</v>
       </c>
       <c r="O54" t="n">
         <v>2.14</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>8.16</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45687.55208333334</v>
+        <v>45688.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>1524</v>
+        <v>1542</v>
       </c>
       <c r="I55" t="n">
         <v>1525.074501695738</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K55" t="n">
-        <v>10.12</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="L55" t="n">
         <v>3.98</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>7.28</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45698.55208333334</v>
+        <v>45699.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>1560</v>
+        <v>1501.5</v>
       </c>
       <c r="I56" t="n">
         <v>1502.230728576323</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K56" t="n">
-        <v>1.17</v>
+        <v>-2.63</v>
       </c>
       <c r="L56" t="n">
-        <v>1.78</v>
+        <v>2.69</v>
       </c>
       <c r="M56" t="n">
         <v>0.93</v>
       </c>
       <c r="N56" t="n">
-        <v>1.99</v>
+        <v>3.59</v>
       </c>
       <c r="O56" t="n">
         <v>1.44</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,25 +4352,25 @@
         <v>10.53</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45737.55208333334</v>
+        <v>45740.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>1382.5</v>
+        <v>1425.5</v>
       </c>
       <c r="I57" t="n">
         <v>1392.655074413361</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K57" t="n">
-        <v>7.93</v>
+        <v>5.06</v>
       </c>
       <c r="L57" t="n">
         <v>4.63</v>
       </c>
       <c r="M57" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="N57" t="n">
         <v>3.44</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>8.18</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45750.55208333334</v>
+        <v>45751.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>1346</v>
+        <v>1283.5</v>
       </c>
       <c r="I58" t="n">
         <v>1344.663374175538</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K58" t="n">
-        <v>-5.58</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="L58" t="n">
-        <v>7.12</v>
+        <v>10.35</v>
       </c>
       <c r="M58" t="n">
         <v>0.35</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>10.98</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>1310</v>
+        <v>1345.5</v>
       </c>
       <c r="I59" t="n">
         <v>1340.73686706447</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>11</v>
       </c>
       <c r="K59" t="n">
-        <v>-2.06</v>
+        <v>-4.83</v>
       </c>
       <c r="L59" t="n">
-        <v>4.64</v>
+        <v>6.16</v>
       </c>
       <c r="M59" t="n">
         <v>3.74</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>9.539999999999999</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45785.38541666666</v>
+        <v>45785.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>1386</v>
+        <v>1341.5</v>
       </c>
       <c r="I60" t="n">
         <v>1356.013996537634</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K60" t="n">
-        <v>3.01</v>
+        <v>-0.3</v>
       </c>
       <c r="L60" t="n">
         <v>2.45</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>8.210000000000001</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45786.55208333334</v>
+        <v>45789.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>1396.5</v>
+        <v>1471</v>
       </c>
       <c r="I61" t="n">
         <v>1446.726345474439</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="K61" t="n">
-        <v>-4.1</v>
+        <v>-9.65</v>
       </c>
       <c r="L61" t="n">
-        <v>4.1</v>
+        <v>9.65</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>0.57</v>
       </c>
       <c r="N61" t="n">
-        <v>4.1</v>
+        <v>5.12</v>
       </c>
       <c r="O61" t="n">
         <v>-3.28</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,25 +4697,25 @@
         <v>10.3</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45820.55208333334</v>
+        <v>45821.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>1468.6</v>
+        <v>1451</v>
       </c>
       <c r="I62" t="n">
         <v>1455.396019713512</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.16</v>
+        <v>-1.36</v>
       </c>
       <c r="L62" t="n">
         <v>5.37</v>
       </c>
       <c r="M62" t="n">
-        <v>0.49</v>
+        <v>1.27</v>
       </c>
       <c r="N62" t="n">
         <v>2.72</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>5.59</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45835.38541666666</v>
+        <v>45835.55208333334</v>
       </c>
       <c r="H63" t="n">
-        <v>1521.5</v>
+        <v>1533</v>
       </c>
       <c r="I63" t="n">
         <v>1532.066211819368</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K63" t="n">
-        <v>-4.86</v>
+        <v>-5.65</v>
       </c>
       <c r="L63" t="n">
         <v>5.94</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>6.9</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45848.38541666666</v>
+        <v>45848.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>1430.4</v>
+        <v>1420</v>
       </c>
       <c r="I64" t="n">
         <v>1427.17468673972</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>12.83333333333333</v>
+        <v>13</v>
       </c>
       <c r="K64" t="n">
-        <v>-6.69</v>
+        <v>-7.37</v>
       </c>
       <c r="L64" t="n">
         <v>8.41</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>5.71</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45859.55208333334</v>
+        <v>45860.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>1405.8</v>
+        <v>1461.2</v>
       </c>
       <c r="I65" t="n">
         <v>1429.247572389159</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K65" t="n">
-        <v>1</v>
+        <v>-2.9</v>
       </c>
       <c r="L65" t="n">
-        <v>0.77</v>
+        <v>3.22</v>
       </c>
       <c r="M65" t="n">
         <v>0.53</v>
       </c>
       <c r="N65" t="n">
-        <v>3.14</v>
+        <v>3.93</v>
       </c>
       <c r="O65" t="n">
         <v>-0.84</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>7.22</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45863.55208333334</v>
+        <v>45866.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>1439</v>
+        <v>1403.3</v>
       </c>
       <c r="I66" t="n">
         <v>1404.801363981933</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K66" t="n">
-        <v>-1.52</v>
+        <v>-3.96</v>
       </c>
       <c r="L66" t="n">
-        <v>3.91</v>
+        <v>4.21</v>
       </c>
       <c r="M66" t="n">
-        <v>0.37</v>
+        <v>0.63</v>
       </c>
       <c r="N66" t="n">
-        <v>1.51</v>
+        <v>1.67</v>
       </c>
       <c r="O66" t="n">
         <v>3.93</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>5.94</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45888.55208333334</v>
+        <v>45889.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>1374.1</v>
+        <v>1390</v>
       </c>
       <c r="I67" t="n">
         <v>1388.229998728202</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K67" t="n">
-        <v>2.08</v>
+        <v>0.95</v>
       </c>
       <c r="L67" t="n">
         <v>2.04</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>6.7</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45925.55208333334</v>
+        <v>45926.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>1357.8</v>
+        <v>1325.8</v>
       </c>
       <c r="I68" t="n">
         <v>1344.31605087738</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K68" t="n">
-        <v>-2.32</v>
+        <v>-4.62</v>
       </c>
       <c r="L68" t="n">
         <v>4.72</v>
@@ -4317,7 +5132,7 @@
         <v>0.66</v>
       </c>
       <c r="N68" t="n">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="O68" t="n">
         <v>1.59</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>7.38</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45936.38541666666</v>
+        <v>45936.55208333334</v>
       </c>
       <c r="H69" t="n">
-        <v>1365.5</v>
+        <v>1380.5</v>
       </c>
       <c r="I69" t="n">
         <v>1380.461150941208</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K69" t="n">
-        <v>-2.99</v>
+        <v>-4.13</v>
       </c>
       <c r="L69" t="n">
-        <v>3.09</v>
+        <v>5.14</v>
       </c>
       <c r="M69" t="n">
         <v>0.43</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,22 +5249,22 @@
         <v>5.26</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45947.55208333334</v>
+        <v>45950.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>1330.1</v>
+        <v>1314.7</v>
       </c>
       <c r="I70" t="n">
         <v>1318.199990051449</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>11</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K70" t="n">
-        <v>-3.65</v>
+        <v>-4.77</v>
       </c>
       <c r="L70" t="n">
-        <v>4.58</v>
+        <v>4.94</v>
       </c>
       <c r="M70" t="n">
         <v>0.29</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,28 +5318,28 @@
         <v>5.32</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45951.57291666666</v>
+        <v>45953.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>1315.9</v>
+        <v>1376.4</v>
       </c>
       <c r="I71" t="n">
         <v>1368.035151513592</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.1875</v>
+        <v>3</v>
       </c>
       <c r="K71" t="n">
-        <v>-0.09</v>
+        <v>-4.69</v>
       </c>
       <c r="L71" t="n">
-        <v>1.85</v>
+        <v>5.84</v>
       </c>
       <c r="M71" t="n">
         <v>0.95</v>
       </c>
       <c r="N71" t="n">
-        <v>0.34</v>
+        <v>5.18</v>
       </c>
       <c r="O71" t="n">
         <v>-1.4</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S71" t="b">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>6.62</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45967.38541666666</v>
+        <v>45967.55208333334</v>
       </c>
       <c r="H72" t="n">
-        <v>1336</v>
+        <v>1327</v>
       </c>
       <c r="I72" t="n">
         <v>1329.325351190569</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K72" t="n">
-        <v>-2.94</v>
+        <v>-3.59</v>
       </c>
       <c r="L72" t="n">
         <v>4.29</v>
@@ -4554,7 +5417,19 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>5.26</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45994.55208333334</v>
+        <v>45995.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>1377.1</v>
+        <v>1397.2</v>
       </c>
       <c r="I73" t="n">
         <v>1386.302308480505</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>27</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K73" t="n">
-        <v>-3.78</v>
+        <v>-5.29</v>
       </c>
       <c r="L73" t="n">
         <v>5.71</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,22 +5525,22 @@
         <v>5.52</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46009.55208333334</v>
+        <v>46010.38541666666</v>
       </c>
       <c r="H74" t="n">
-        <v>1332.8</v>
+        <v>1325</v>
       </c>
       <c r="I74" t="n">
         <v>1330.847781394838</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K74" t="n">
-        <v>-4.61</v>
+        <v>-5.17</v>
       </c>
       <c r="L74" t="n">
-        <v>5.14</v>
+        <v>5.34</v>
       </c>
       <c r="M74" t="n">
         <v>1.36</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>4.59</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46105.55208333334</v>
+        <v>46106.38541666666</v>
       </c>
       <c r="H75" t="n">
-        <v>991.6</v>
+        <v>1011.8</v>
       </c>
       <c r="I75" t="n">
         <v>1002.282873369692</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>95.16666666666667</v>
+        <v>96</v>
       </c>
       <c r="K75" t="n">
-        <v>25.16</v>
+        <v>23.64</v>
       </c>
       <c r="L75" t="n">
         <v>4.83</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>130</v>
+        <v>131</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>4</v>
+      </c>
+      <c r="U75" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>7.17</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46135.55208333334</v>
+        <v>46136.38541666666</v>
       </c>
       <c r="H76" t="n">
-        <v>1020</v>
+        <v>985.5</v>
       </c>
       <c r="I76" t="n">
         <v>1015.292014806974</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K76" t="n">
-        <v>0.8100000000000001</v>
+        <v>-2.6</v>
       </c>
       <c r="L76" t="n">
         <v>5.98</v>
@@ -4773,7 +5684,7 @@
         <v>1.53</v>
       </c>
       <c r="N76" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="O76" t="n">
         <v>0.54</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4809,19 +5732,19 @@
         <v>8.210000000000001</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46167.55208333334</v>
+        <v>46168.38541666666</v>
       </c>
       <c r="H77" t="n">
-        <v>936.4</v>
+        <v>979.65</v>
       </c>
       <c r="I77" t="n">
         <v>971.8289453908235</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K77" t="n">
-        <v>4.98</v>
+        <v>0.59</v>
       </c>
       <c r="L77" t="n">
         <v>3.86</v>
@@ -4830,7 +5753,7 @@
         <v>1.13</v>
       </c>
       <c r="N77" t="n">
-        <v>4.51</v>
+        <v>4.94</v>
       </c>
       <c r="O77" t="n">
         <v>-2.94</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -4866,19 +5801,19 @@
         <v>10.21</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46269.55208333334</v>
+        <v>46272.38541666666</v>
       </c>
       <c r="H78" t="n">
-        <v>1318</v>
+        <v>1286.1</v>
       </c>
       <c r="I78" t="n">
         <v>1297.654796842944</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>101.1666666666667</v>
+        <v>104</v>
       </c>
       <c r="K78" t="n">
-        <v>34.54</v>
+        <v>31.28</v>
       </c>
       <c r="L78" t="n">
         <v>4.34</v>
@@ -4896,7 +5831,19 @@
         <v>1</v>
       </c>
       <c r="Q78" t="n">
-        <v>144</v>
+        <v>145</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>4</v>
+      </c>
+      <c r="U78" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="79">
@@ -4947,6 +5894,14 @@
       <c r="Q79" t="n">
         <v>68</v>
       </c>
+      <c r="R79" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7049,7 +8004,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.9</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="6">
@@ -7059,7 +8014,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -7069,7 +8024,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>101.2</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8">
@@ -7079,7 +8034,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -7089,7 +8044,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29.2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10">
@@ -7099,7 +8054,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11">
@@ -7109,7 +8064,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12">
@@ -7119,7 +8074,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
@@ -7129,7 +8084,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>76.59999999999999</v>
+        <v>75.3</v>
       </c>
     </row>
     <row r="14">
@@ -7139,7 +8094,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.25</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="15">
@@ -7149,7 +8104,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.68</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="16">
@@ -7159,7 +8114,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.82</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="17">
@@ -7169,7 +8124,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>34.54</v>
+        <v>31.28</v>
       </c>
     </row>
     <row r="18">
@@ -7179,7 +8134,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>44.2</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="19">
@@ -7189,7 +8144,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.23</v>
+        <v>5.34</v>
       </c>
     </row>
     <row r="20">
@@ -7199,7 +8154,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.98</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="21">
@@ -7209,7 +8164,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10.13</v>
+        <v>12.53</v>
       </c>
     </row>
     <row r="22">
@@ -7219,7 +8174,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23">
@@ -7229,7 +8184,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -7239,7 +8194,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="25">
@@ -7259,7 +8214,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.07</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="27">
@@ -7269,7 +8224,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.05</v>
+        <v>11.72</v>
       </c>
     </row>
     <row r="28">
@@ -7279,7 +8234,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29">
